--- a/Log.xlsx
+++ b/Log.xlsx
@@ -1,133 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CUB_LOG\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F59B2BF-3B2D-4F58-88FE-3641C27353C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
-  <si>
-    <t>reg_no</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>problem_statement</t>
-  </si>
-  <si>
-    <t>problem_no</t>
-  </si>
-  <si>
-    <t>faculty_guide</t>
-  </si>
-  <si>
-    <t>faculty_id</t>
-  </si>
-  <si>
-    <t>selvakumaran</t>
-  </si>
-  <si>
-    <t>HR chatbot</t>
-  </si>
-  <si>
-    <t>Brindha</t>
-  </si>
-  <si>
-    <t>F101</t>
-  </si>
-  <si>
-    <t>Ram</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>start_time</t>
-  </si>
-  <si>
-    <t>end_time</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>faculty</t>
-  </si>
-  <si>
-    <t>03:30:00</t>
-  </si>
-  <si>
-    <t>05:30:00</t>
-  </si>
-  <si>
-    <t>Ollama model practice session</t>
-  </si>
-  <si>
-    <t>127156129</t>
-  </si>
-  <si>
-    <t>05:00:00</t>
-  </si>
-  <si>
-    <t>abcd</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>12345</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -165,36 +90,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -514,76 +505,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="49.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" customWidth="1"/>
-    <col min="5" max="5" width="30.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.77734375" customWidth="1"/>
+    <col width="16.77734375" customWidth="1" min="1" max="1"/>
+    <col width="36.33203125" customWidth="1" min="2" max="2"/>
+    <col width="49.33203125" customWidth="1" min="3" max="3"/>
+    <col width="17.5546875" customWidth="1" min="4" max="4"/>
+    <col width="30.6640625" customWidth="1" min="5" max="5"/>
+    <col width="32.77734375" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>reg_no</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>problem_statement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>problem_no</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>faculty_guide</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>faculty_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>127156146</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>selvakumaran</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HR chatbot</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Brindha</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>F101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ram</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HR chatbot</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>127156129</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Brindha</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>F101</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -592,80 +615,2028 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="17.6640625" style="4" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>reg_no</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>start_time</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>end_time</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>faculty</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>127156146</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>selvakumaran</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>46069</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>03:30:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>05:30:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ollama model practice session</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Brindha</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ram</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
         <v>46069</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>03:30:00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>05:00:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>abcd</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brindha</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127156146</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>selvakumaran</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>46079</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>08:02:00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Eat five star</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Brindha</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127156146</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>selvakumaran</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>46079</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Done 1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Brindha</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127156134</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rishi Grace.M</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>46079</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Modified the Log Portal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>46079</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10:26:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Five star eating</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10:31:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12:15:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>did nothing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>vd</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>vdcdcd</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>vdcdcdcdcd</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>cdcdc</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>cdcdc</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>cdcdc</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>cdcdc</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>cdcdc</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>cdcdc</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>cdcdc</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>cdcdc</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>cdcdc.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>10:34:00</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10:34:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>10:34:00</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>10:34:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>10:34:00</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10:34:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>10:34:00</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>10:34:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>vfdbf</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127156050</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Harrish.A.R</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>15:15:00</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>llll</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127156134</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rishi Grace.M</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>19:03:00</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tuning the login portal</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127156134</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Rishi Grace.M</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>19:10:00</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data hub: 
+a place where maintain the data which is prepared for AI training.
+Virtualized dataset pointing to actual DW, (connected) used for Ai needs
+Meta data is stored.
+Entire data lineage is stored (where did the data come? what are the changes we implemented? in which pipeline it is used? etc,. like data cleaning, improvement)
+Data canvas: 
+The annotation platform, enrichment of dataset can be done. 
+LARGE LABS?
+AI Workbench: 
+AI can govern using (ex: NIST framework) to know whether we follow the policies related to CUB or RBI.
+GenAI Studio: 
+3 main services
+Data manipulation: data ETL operations
+Model AI: The model is available 
+Algo-Type AI
+</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127156050</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Harrish.A.R</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>19:16:00</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19:16:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data hub: 
+a place where maintain the data which is prepared for AI training.
+Virtualized dataset pointing to actual DW, (connected) used for Ai needs
+Meta data is stored.
+Entire data lineage is stored (where did the data come? what are the changes we implemented? in which pipeline it is used? etc,. like data cleaning, improvement)
+Data canvas: 
+The annotation platform, enrichment of dataset can be done. 
+LARGE LABS?
+AI Workbench: 
+AI can govern using (ex: NIST framework) to know whether we follow the policies related to CUB or RBI.
+GenAI Studio: 
+3 main services
+Data manipulation: data ETL operations
+Model AI: The model is available 
+Algo-Type AI
+</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ram Aditya.R</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>08:59:00</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Centific</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127156037</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sivapriya.G.S</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>09:14:00</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Unsupervised clustering</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dr.Srilakshmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127156037</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sivapriya.G.S</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>09:14:00</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Unsupervised clustering +2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dr.Srilakshmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127156136</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kishore.S</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>09:15:00</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Banking Terms</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dr.Jeyasheela Rakini</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127014013</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Calvin Gabriel</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>09:16:00</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Early waring Systems</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dr.Premalatha</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>127156020</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Barath Vishnu.J</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>08:45:00</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>10:42:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>discussion on banking terms</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -674,30 +2645,144 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>faculty_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>F101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Brindha</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>f101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Leo das</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C1613</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brindha G R</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cubcoe</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>f102</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mr Grace</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>f103</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mrgrace</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>f104</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Eddie</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>qwerty</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>f105</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Harry</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Log.xlsx
+++ b/Log.xlsx
@@ -9,6 +9,8 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Active_Sessions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Student_Hours" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -17,10 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -100,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -112,7 +113,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,7 +671,7 @@
           <t>selvakumaran</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>46069</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -702,7 +704,7 @@
           <t>Ram</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>46069</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -735,7 +737,7 @@
           <t>selvakumaran</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>46079</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -768,7 +770,7 @@
           <t>selvakumaran</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>46079</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -801,7 +803,7 @@
           <t>Rishi Grace.M</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>46079</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -834,7 +836,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>46079</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -867,7 +869,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -900,7 +902,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -933,7 +935,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -966,7 +968,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -999,7 +1001,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -1032,7 +1034,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1065,7 +1067,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -1098,7 +1100,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -1131,7 +1133,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -1164,7 +1166,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -1197,7 +1199,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1230,7 +1232,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1263,7 +1265,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1296,7 +1298,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1329,7 +1331,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1362,7 +1364,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1395,7 +1397,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1428,7 +1430,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -1461,7 +1463,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -1494,7 +1496,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -1527,7 +1529,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -1560,7 +1562,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -1593,7 +1595,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -1626,7 +1628,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -1659,7 +1661,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -1692,7 +1694,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -1725,7 +1727,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -1758,7 +1760,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -1791,7 +1793,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -1824,7 +1826,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -1857,7 +1859,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -1890,7 +1892,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -1923,7 +1925,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -1956,7 +1958,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -1989,7 +1991,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -2022,7 +2024,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -2055,7 +2057,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -2088,7 +2090,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -2121,7 +2123,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -2154,7 +2156,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -2187,7 +2189,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -2220,7 +2222,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -2253,7 +2255,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="6" t="n">
         <v>46083</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -2286,7 +2288,7 @@
           <t>Harrish.A.R</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="6" t="n">
         <v>46085</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -2319,7 +2321,7 @@
           <t>Rishi Grace.M</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C52" s="6" t="n">
         <v>46085</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -2352,7 +2354,7 @@
           <t>Rishi Grace.M</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="6" t="n">
         <v>46085</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -2400,7 +2402,7 @@
           <t>Harrish.A.R</t>
         </is>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="6" t="n">
         <v>46085</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -2448,7 +2450,7 @@
           <t>Ram Aditya.R</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="6" t="n">
         <v>46086</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -2481,7 +2483,7 @@
           <t>Sivapriya.G.S</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="6" t="n">
         <v>46086</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -2514,7 +2516,7 @@
           <t>Sivapriya.G.S</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="6" t="n">
         <v>46086</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -2547,7 +2549,7 @@
           <t>Kishore.S</t>
         </is>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="6" t="n">
         <v>46086</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -2580,7 +2582,7 @@
           <t>Calvin Gabriel</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="6" t="n">
         <v>46086</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -2605,17 +2607,15 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>127156020</t>
-        </is>
+      <c r="A60" t="n">
+        <v>127156020</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Barath Vishnu.J</t>
         </is>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="6" t="n">
         <v>46086</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -2634,6 +2634,239 @@
         </is>
       </c>
       <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127156146</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Selvakumaran.B</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>46109</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>12:42:14</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>12:45:10</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Onnum panla</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127156134</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rishi Grace.M</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>46109</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>12:37:08</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>12:46:56</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Naanum athe thaan</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127156019</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Abhishek Perumal.B</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>46109</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>13:51:36</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>13:52:34</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>abcdefg</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dr.G.Manikandan</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126156128</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sailesh S</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>46109</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>14:02:01</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>14:04:17</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>agfADF/QE</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Brindha.G.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127156134</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Rishi Grace.M</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>46110</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>18:45:16</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>18:46:31</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127156050</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Harrish.A.R</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>46110</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>13:12:13</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>18:46:58</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>127156146</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Selvakumaran.B</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>46111</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>14:26:41</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>14:27:47</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>hello boi</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">Dr.G.R.Brindha </t>
         </is>
@@ -2788,4 +3021,151 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>reg_no</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>faculty</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>problem_no</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>start_time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>reg_no</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>total_hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>127156146</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Selvakumaran.B</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.06759712138888889</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>127156134</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rishi Grace.M</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1844568611111111</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>127156019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Abhishek Perumal.B</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0162657625</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>126156128</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sailesh S</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03795537750000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>127156050</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Harrish.A.R</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>29.57926353388889</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Log.xlsx
+++ b/Log.xlsx
@@ -622,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2838,10 +2838,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>127156146</t>
-        </is>
+      <c r="A67" t="n">
+        <v>127156146</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2867,6 +2865,41 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>127156146</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Selvakumaran.B</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>46111</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>16:31:37</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>16:36:21</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>suthine irupen</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">Dr.G.R.Brindha </t>
         </is>
@@ -3029,7 +3062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3056,6 +3089,33 @@
       <c r="E1" s="4" t="inlineStr">
         <is>
           <t>start_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>127156146</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Selvakumaran.B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:01:10</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3162,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06759712138888889</v>
+        <v>0.1465330144444444</v>
       </c>
     </row>
     <row r="3">

--- a/Log.xlsx
+++ b/Log.xlsx
@@ -1,115 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CUB_LOG\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9650D573-417C-4D64-8921-B802D6BDDF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Active_Sessions" sheetId="4" r:id="rId4"/>
-    <sheet name="Student_Hours" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Active_Sessions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Student_Hours" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
-  <si>
-    <t>reg_no</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>total_hours</t>
-  </si>
-  <si>
-    <t>problem_statement</t>
-  </si>
-  <si>
-    <t>problem_no</t>
-  </si>
-  <si>
-    <t>faculty_guide</t>
-  </si>
-  <si>
-    <t>faculty_id</t>
-  </si>
-  <si>
-    <t>selvakumaran</t>
-  </si>
-  <si>
-    <t>HR chatbot</t>
-  </si>
-  <si>
-    <t>Brindha</t>
-  </si>
-  <si>
-    <t>F101</t>
-  </si>
-  <si>
-    <t>Ram</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>start_time</t>
-  </si>
-  <si>
-    <t>end_time</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>faculty</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -132,30 +71,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -475,76 +484,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="49.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" customWidth="1"/>
-    <col min="5" max="5" width="30.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.77734375" customWidth="1"/>
+    <col width="16.77734375" customWidth="1" min="1" max="1"/>
+    <col width="36.33203125" customWidth="1" min="2" max="2"/>
+    <col width="49.33203125" customWidth="1" min="3" max="3"/>
+    <col width="17.5546875" customWidth="1" min="4" max="4"/>
+    <col width="30.6640625" customWidth="1" min="5" max="5"/>
+    <col width="32.77734375" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>reg_no</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>problem_statement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>problem_no</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>faculty_guide</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>faculty_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>127156146</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>selvakumaran</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HR chatbot</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>127156146</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Brindha</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>F101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127156129</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ram</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HR chatbot</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>127156129</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Brindha</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>F101</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -553,35 +594,85 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C2" s="1"/>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>reg_no</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>start_time</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>end_time</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>faculty</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>127156146</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Selvakumaran.B</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>17:50:40</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>18:00:34</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>abcdefg</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr.G.R.Brindha </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -589,19 +680,29 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>17</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>faculty_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -610,25 +711,39 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>13</v>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>reg_no</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>faculty</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>problem_no</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>start_time</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -637,19 +752,44 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>reg_no</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>total_hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>127156146</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Selvakumaran.B</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1650614322222222</v>
       </c>
     </row>
   </sheetData>
